--- a/artfynd/A 3193-2026 artfynd.xlsx
+++ b/artfynd/A 3193-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,129 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133593001</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58468</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norr sjön Lössnaren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>610643</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6759867</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hans Sandblom</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Sandblom</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3193-2026 artfynd.xlsx
+++ b/artfynd/A 3193-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133593001</v>
       </c>
       <c r="B3" t="n">
-        <v>58468</v>
+        <v>58475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3193-2026 artfynd.xlsx
+++ b/artfynd/A 3193-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133593001</v>
       </c>
       <c r="B3" t="n">
-        <v>58475</v>
+        <v>58485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3193-2026 artfynd.xlsx
+++ b/artfynd/A 3193-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>109267222</v>
       </c>
       <c r="B2" t="n">
-        <v>57538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -799,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133593001</v>
+        <v>103677844</v>
       </c>
       <c r="B3" t="n">
-        <v>58485</v>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,18 +824,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -880,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,6 +910,248 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109267233</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norr sjön Lössnaren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>610643</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6759867</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Sandblom</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Sandblom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133593001</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58485</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr sjön Lössnaren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>610643</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6759867</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Sandblom</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Sandblom</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3193-2026 artfynd.xlsx
+++ b/artfynd/A 3193-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109267222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103677844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109267233</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,8 +1172,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133593001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>